--- a/2_Formulas_Functions/8_Text_Functions.xlsx
+++ b/2_Formulas_Functions/8_Text_Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Developer\_Courses\Excel\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f943803864469b1e/Documents/GitHub/Excel_Data_Analytics/Excel_project_data_analysis/2_Formulas_Functions/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289F5FEB-D4A0-4E30-9E0C-8AA9F558B1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11993" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="795" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="8" r:id="rId1"/>
@@ -1785,27 +1785,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B5E7F13-C613-4452-9CDB-2C26D6876D9D}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" customWidth="1"/>
-    <col min="2" max="2" width="14.265625" customWidth="1"/>
-    <col min="3" max="3" width="27.265625" customWidth="1"/>
-    <col min="4" max="4" width="17.59765625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="26.265625" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.21875" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="26.21875" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="8.86328125" customWidth="1"/>
-    <col min="10" max="10" width="34.73046875" customWidth="1"/>
-    <col min="11" max="11" width="8.86328125" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" customWidth="1"/>
+    <col min="10" max="10" width="34.77734375" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" customWidth="1"/>
     <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="13" max="13" width="15.46484375" customWidth="1"/>
-    <col min="14" max="14" width="8.86328125" customWidth="1"/>
-    <col min="15" max="15" width="16.3984375" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" customWidth="1"/>
+    <col min="15" max="15" width="16.44140625" customWidth="1"/>
     <col min="17" max="19" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -1853,7 +1853,7 @@
       <c r="U1" s="17"/>
       <c r="V1" s="17"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>NY</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -2629,21 +2629,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BCB134-41DE-47D5-9456-1C60C9867AFA}">
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="3" width="27.265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.59765625" customWidth="1"/>
+    <col min="3" max="3" width="27.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="29.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>457 Oak St San Jose, CA, 95101</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>203 Birch St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>790 Pine St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>457 Oak St San Jose, CA, 95101</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>790 Pine St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>123 Elm St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>123 Elm St Los Angeles, CA, 90001</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>123 Elm St San Diego, CA, 92101</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>202 Birch St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>123 Elm St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>456 Oak St Chicago, IL, 60601</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>203 Birch St Chicago, IL, 60602</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>456 Oak St New York, NY, 10001</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -3280,23 +3280,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F197DD-EE87-4022-A4E6-1027B6E64DD6}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29" style="9" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="11.86328125" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.21875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>0123548</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>0123549</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>0123550</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>0123551</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>0123552</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>0123553</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>0123554</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>0123555</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>0123556</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>0123557</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>0123558</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -3846,7 +3846,7 @@
         <v>0123559</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>0123560</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>0123561</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -3969,7 +3969,7 @@
         <v>0123562</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>0123563</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>0123564</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>0123565</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>0123566</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -4182,21 +4182,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E73CB36-69AF-4B27-BCC8-FDB353A4DE72}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.1328125" customWidth="1"/>
-    <col min="5" max="5" width="26.1328125" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" customWidth="1"/>
     <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="40" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.59765625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="9.1328125" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -4227,7 +4227,7 @@
       <c r="K1" s="17"/>
       <c r="L1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>72</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>71</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>74</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>76</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>77</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>78</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>80</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>CA</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>82</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>83</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>85</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>IL</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>NY</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>PA</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -4998,30 +4998,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85789AE4-586B-4DA1-B069-1172780CDADC}">
   <dimension ref="A2:BW25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.3984375" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>94</v>
       </c>
       <c r="B2" s="16"/>
     </row>
-    <row r="3" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>_xlfn.TEXTJOIN(", ",TRUE,Data!H2:H21)</f>
         <v>Kafka, DataBricks, Spark, Python, GCP, Power BI, GCP, Airflow, Hadoop, R, Azure, Java, SQL, DataBricks, Kafka, DataBricks, Spark, Python, GCP, DataBricks, Hadoop, Java, Snowflake, Airflow, DataBricks, Azure, Java, SQL, DataBricks, Snowflake, Airflow, DataBricks, Scala, Azure, R, Kafka, Snowflake, Excel, Scala, Excel, Power BI, R, Scala, R, Hadoop, Power BI, SQL, Snowflake, Airflow, DataBricks, Java, Scala, R, DataBricks, Azure, Scala, Power BI, GCP, Airflow, Hadoop, R, DataBricks, Hadoop, Java, Snowflake, Power BI, Tableau, Airflow, SQL, DataBricks, Hadoop, Java, DataBricks, Hadoop, Java</v>
       </c>
     </row>
-    <row r="5" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>67</v>
       </c>
       <c r="B5" s="16"/>
     </row>
-    <row r="6" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A6" t="str" cm="1">
         <f t="array" ref="A6:BW6">_xlfn.TEXTSPLIT(A3,", ")</f>
         <v>Kafka</v>
@@ -5249,7 +5249,7 @@
         <v>Java</v>
       </c>
     </row>
-    <row r="8" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>68</v>
       </c>
@@ -5261,7 +5261,7 @@
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
     </row>
-    <row r="9" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str" cm="1">
         <f t="array" ref="A9:A25">_xlfn.UNIQUE(TRANSPOSE(6:6))</f>
         <v>Kafka</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <v>DataBricks</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <v>Spark</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <v>Python</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
         <v>GCP</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
         <v>Power BI</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
         <v>Airflow</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="str">
         <v>Hadoop</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="str">
         <v>R</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="str">
         <v>Azure</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="str">
         <v>Java</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="str">
         <v>SQL</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="str">
         <v>Snowflake</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="str">
         <v>Scala</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="str">
         <v>Excel</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="str">
         <v>Tableau</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>0</v>
       </c>
